--- a/ksoft/docs/fields_details/jalmeida/CE0302(2).xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302(2).xlsx
@@ -9869,13 +9869,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71016296-6FC5-4B54-8209-1EEE46A00E4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D12B25F-7F2F-48F2-A671-9E53FECB18AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9F64C2-902B-4E82-9589-554549BD1553}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E47B5E7-A18B-43EA-AD26-8DA922B9357A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4032946-B1FC-4376-BCF9-955418C49119}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CF73774-FC41-4C80-895F-7E907ECED32E}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/CE0302(2).xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302(2).xlsx
@@ -9869,13 +9869,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D12B25F-7F2F-48F2-A671-9E53FECB18AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71016296-6FC5-4B54-8209-1EEE46A00E4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E47B5E7-A18B-43EA-AD26-8DA922B9357A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9F64C2-902B-4E82-9589-554549BD1553}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CF73774-FC41-4C80-895F-7E907ECED32E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4032946-B1FC-4376-BCF9-955418C49119}"/>
 </file>